--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_biobio.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2022_biobio.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>22.50893587118832</v>
+      </c>
+      <c r="C2">
         <v>33.1313049412496</v>
-      </c>
-      <c r="C2">
-        <v>22.50893587118832</v>
       </c>
       <c r="D2">
         <v>3.018293429049231</v>
       </c>
       <c r="E2">
-        <v>21.28710722131055</v>
+        <v>14.46215692914138</v>
       </c>
       <c r="F2">
         <v>64.25073584954806</v>
       </c>
       <c r="G2">
-        <v>14.46215692914138</v>
+        <v>21.28710722131055</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>31.35164298743673</v>
+      </c>
+      <c r="C3">
         <v>29.55065128587211</v>
-      </c>
-      <c r="C3">
-        <v>31.35164298743673</v>
       </c>
       <c r="D3">
         <v>3.384020170405147</v>
       </c>
       <c r="E3">
-        <v>18.36558727725618</v>
+        <v>19.48489493517277</v>
       </c>
       <c r="F3">
         <v>62.14951778757106</v>
       </c>
       <c r="G3">
-        <v>19.48489493517277</v>
+        <v>18.36558727725618</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>26.27194393793128</v>
+      </c>
+      <c r="C4">
         <v>33.95902606457149</v>
-      </c>
-      <c r="C4">
-        <v>26.27194393793128</v>
       </c>
       <c r="D4">
         <v>2.94472520530638</v>
       </c>
       <c r="E4">
-        <v>21.19379671984827</v>
+        <v>16.39629588307486</v>
       </c>
       <c r="F4">
         <v>62.40990739707687</v>
       </c>
       <c r="G4">
-        <v>16.39629588307486</v>
+        <v>21.19379671984827</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.88218793828892</v>
+      </c>
+      <c r="C5">
         <v>45.21739130434783</v>
-      </c>
-      <c r="C5">
-        <v>27.88218793828892</v>
       </c>
       <c r="D5">
         <v>2.211538461538462</v>
       </c>
       <c r="E5">
-        <v>26.12218441095447</v>
+        <v>16.10760006481931</v>
       </c>
       <c r="F5">
         <v>57.77021552422622</v>
       </c>
       <c r="G5">
-        <v>16.10760006481932</v>
+        <v>26.12218441095446</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.66994586413644</v>
+      </c>
+      <c r="C6">
         <v>30.35100995401362</v>
-      </c>
-      <c r="C6">
-        <v>29.66994586413644</v>
       </c>
       <c r="D6">
         <v>3.294783275795934</v>
       </c>
       <c r="E6">
-        <v>18.96689705347399</v>
+        <v>18.54128774099673</v>
       </c>
       <c r="F6">
         <v>62.49181520552929</v>
       </c>
       <c r="G6">
-        <v>18.54128774099673</v>
+        <v>18.96689705347399</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>27.64430577223089</v>
+      </c>
+      <c r="C7">
         <v>37.53163459871728</v>
-      </c>
-      <c r="C7">
-        <v>27.64430577223089</v>
       </c>
       <c r="D7">
         <v>2.664418991317199</v>
       </c>
       <c r="E7">
-        <v>22.72221639206632</v>
+        <v>16.73627872809319</v>
       </c>
       <c r="F7">
         <v>60.54150487984048</v>
       </c>
       <c r="G7">
-        <v>16.73627872809319</v>
+        <v>22.72221639206632</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>28.84797132149259</v>
+      </c>
+      <c r="C8">
         <v>35.66889359621965</v>
-      </c>
-      <c r="C8">
-        <v>28.84797132149259</v>
       </c>
       <c r="D8">
         <v>2.803563270899954</v>
       </c>
       <c r="E8">
-        <v>21.68099520621212</v>
+        <v>17.53496295709362</v>
       </c>
       <c r="F8">
         <v>60.78404183669426</v>
       </c>
       <c r="G8">
-        <v>17.53496295709362</v>
+        <v>21.68099520621212</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>31.06228014792099</v>
+      </c>
+      <c r="C9">
         <v>24.76098132948498</v>
-      </c>
-      <c r="C9">
-        <v>31.06228014792099</v>
       </c>
       <c r="D9">
         <v>4.038612148256079</v>
       </c>
       <c r="E9">
+        <v>19.93430239709425</v>
+      </c>
+      <c r="F9">
+        <v>64.17527078554942</v>
+      </c>
+      <c r="G9">
         <v>15.89042681735632</v>
-      </c>
-      <c r="F9">
-        <v>64.17527078554943</v>
-      </c>
-      <c r="G9">
-        <v>19.93430239709426</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.54588796185936</v>
+      </c>
+      <c r="C10">
         <v>36.66070719110051</v>
-      </c>
-      <c r="C10">
-        <v>28.54588796185936</v>
       </c>
       <c r="D10">
         <v>2.727716066106746</v>
       </c>
       <c r="E10">
-        <v>22.19082546744423</v>
+        <v>17.27890338483737</v>
       </c>
       <c r="F10">
         <v>60.53027114771839</v>
       </c>
       <c r="G10">
-        <v>17.27890338483737</v>
+        <v>22.19082546744423</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>26.55554034559373</v>
+      </c>
+      <c r="C11">
         <v>38.61973106447503</v>
-      </c>
-      <c r="C11">
-        <v>26.55554034559373</v>
       </c>
       <c r="D11">
         <v>2.589349983640528</v>
       </c>
       <c r="E11">
-        <v>23.38106106004004</v>
+        <v>16.07718886664712</v>
       </c>
       <c r="F11">
         <v>60.54175007331285</v>
       </c>
       <c r="G11">
-        <v>16.07718886664712</v>
+        <v>23.38106106004004</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.38733235220615</v>
+      </c>
+      <c r="C12">
         <v>39.4746341598867</v>
-      </c>
-      <c r="C12">
-        <v>27.38733235220615</v>
       </c>
       <c r="D12">
         <v>2.533272369161508</v>
       </c>
       <c r="E12">
-        <v>23.65705917593024</v>
+        <v>16.41316647806696</v>
       </c>
       <c r="F12">
         <v>59.92977434600279</v>
       </c>
       <c r="G12">
-        <v>16.41316647806696</v>
+        <v>23.65705917593024</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>26.06783373607079</v>
+      </c>
+      <c r="C13">
         <v>34.97557498739634</v>
-      </c>
-      <c r="C13">
-        <v>26.06783373607079</v>
       </c>
       <c r="D13">
         <v>2.859138128137581</v>
       </c>
       <c r="E13">
-        <v>21.71810399732288</v>
+        <v>16.18683679307404</v>
       </c>
       <c r="F13">
         <v>62.09505920960309</v>
       </c>
       <c r="G13">
-        <v>16.18683679307404</v>
+        <v>21.71810399732288</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>30.2596869687555</v>
+      </c>
+      <c r="C14">
         <v>30.96312796764171</v>
-      </c>
-      <c r="C14">
-        <v>30.2596869687555</v>
       </c>
       <c r="D14">
         <v>3.229647860658841</v>
       </c>
       <c r="E14">
-        <v>19.20517761698724</v>
+        <v>18.76886157873686</v>
       </c>
       <c r="F14">
         <v>62.0259608042759</v>
       </c>
       <c r="G14">
-        <v>18.76886157873686</v>
+        <v>19.20517761698724</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>29.03974588695227</v>
+      </c>
+      <c r="C15">
         <v>30.63202475973285</v>
-      </c>
-      <c r="C15">
-        <v>29.03974588695227</v>
       </c>
       <c r="D15">
         <v>3.2645572985908</v>
       </c>
       <c r="E15">
-        <v>19.18437093524446</v>
+        <v>18.18715090923003</v>
       </c>
       <c r="F15">
         <v>62.62847815552553</v>
       </c>
       <c r="G15">
-        <v>18.18715090923003</v>
+        <v>19.18437093524446</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>33.10850572631389</v>
+      </c>
+      <c r="C16">
         <v>32.54719116382237</v>
-      </c>
-      <c r="C16">
-        <v>33.10850572631389</v>
       </c>
       <c r="D16">
         <v>3.072461752433936</v>
       </c>
       <c r="E16">
-        <v>19.64749282688892</v>
+        <v>19.98633693127477</v>
       </c>
       <c r="F16">
         <v>60.36617024183631</v>
       </c>
       <c r="G16">
-        <v>19.98633693127477</v>
+        <v>19.64749282688892</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>26.92943120132169</v>
+      </c>
+      <c r="C17">
         <v>36.44087797970262</v>
-      </c>
-      <c r="C17">
-        <v>26.92943120132169</v>
       </c>
       <c r="D17">
         <v>2.744170984455959</v>
       </c>
       <c r="E17">
-        <v>22.30569199653279</v>
+        <v>16.48367523837041</v>
       </c>
       <c r="F17">
         <v>61.21063276509679</v>
       </c>
       <c r="G17">
-        <v>16.48367523837041</v>
+        <v>22.30569199653279</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>28.39741841650759</v>
+      </c>
+      <c r="C18">
         <v>32.39250977183892</v>
-      </c>
-      <c r="C18">
-        <v>28.39741841650759</v>
       </c>
       <c r="D18">
         <v>3.087133436228427</v>
       </c>
       <c r="E18">
-        <v>20.14585747802245</v>
+        <v>17.66119230008197</v>
       </c>
       <c r="F18">
-        <v>62.19295022189559</v>
+        <v>62.19295022189558</v>
       </c>
       <c r="G18">
-        <v>17.66119230008198</v>
+        <v>20.14585747802244</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>32.3924557550704</v>
+      </c>
+      <c r="C19">
         <v>27.92274899883736</v>
-      </c>
-      <c r="C19">
-        <v>32.3924557550704</v>
       </c>
       <c r="D19">
         <v>3.581309275965765</v>
       </c>
       <c r="E19">
+        <v>20.20547945205479</v>
+      </c>
+      <c r="F19">
+        <v>62.37711522965351</v>
+      </c>
+      <c r="G19">
         <v>17.4174053182917</v>
-      </c>
-      <c r="F19">
-        <v>62.3771152296535</v>
-      </c>
-      <c r="G19">
-        <v>20.20547945205479</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>35.13245502195778</v>
+      </c>
+      <c r="C20">
         <v>26.08018132880011</v>
-      </c>
-      <c r="C20">
-        <v>35.13245502195778</v>
       </c>
       <c r="D20">
         <v>3.834329168929929</v>
       </c>
       <c r="E20">
-        <v>16.17750439367311</v>
+        <v>21.79261862917399</v>
       </c>
       <c r="F20">
         <v>62.0298769771529</v>
       </c>
       <c r="G20">
-        <v>21.79261862917399</v>
+        <v>16.17750439367311</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>29.77930558392798</v>
+      </c>
+      <c r="C21">
         <v>29.30593613738985</v>
-      </c>
-      <c r="C21">
-        <v>29.77930558392798</v>
       </c>
       <c r="D21">
         <v>3.412277960723986</v>
       </c>
       <c r="E21">
-        <v>18.42153038226347</v>
+        <v>18.71908749153158</v>
       </c>
       <c r="F21">
         <v>62.85938212620496</v>
       </c>
       <c r="G21">
-        <v>18.71908749153158</v>
+        <v>18.42153038226347</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.31167440199929</v>
+      </c>
+      <c r="C22">
         <v>42.66333452338451</v>
-      </c>
-      <c r="C22">
-        <v>27.31167440199929</v>
       </c>
       <c r="D22">
         <v>2.343933054393305</v>
       </c>
       <c r="E22">
+        <v>16.06805293005671</v>
+      </c>
+      <c r="F22">
+        <v>58.83217811384163</v>
+      </c>
+      <c r="G22">
         <v>25.09976895610166</v>
-      </c>
-      <c r="F22">
-        <v>58.83217811384164</v>
-      </c>
-      <c r="G22">
-        <v>16.06805293005672</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>27.12585856631518</v>
+      </c>
+      <c r="C23">
         <v>31.5904034052433</v>
-      </c>
-      <c r="C23">
-        <v>27.12585856631518</v>
       </c>
       <c r="D23">
         <v>3.165518297351095</v>
       </c>
       <c r="E23">
-        <v>19.90369670557401</v>
+        <v>17.09078718800475</v>
       </c>
       <c r="F23">
         <v>63.00551610642123</v>
       </c>
       <c r="G23">
-        <v>17.09078718800475</v>
+        <v>19.90369670557401</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>28.86006647982794</v>
+      </c>
+      <c r="C24">
         <v>36.2901648960438</v>
-      </c>
-      <c r="C24">
-        <v>28.86006647982794</v>
       </c>
       <c r="D24">
         <v>2.755567528735632</v>
       </c>
       <c r="E24">
-        <v>21.97403212439323</v>
+        <v>17.47503847823513</v>
       </c>
       <c r="F24">
         <v>60.55092939737164</v>
       </c>
       <c r="G24">
-        <v>17.47503847823513</v>
+        <v>21.97403212439323</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>28.4765862558281</v>
+      </c>
+      <c r="C25">
         <v>34.47699168862761</v>
-      </c>
-      <c r="C25">
-        <v>28.4765862558281</v>
       </c>
       <c r="D25">
         <v>2.900485080111715</v>
       </c>
       <c r="E25">
-        <v>21.15755427007526</v>
+        <v>17.47527523791752</v>
       </c>
       <c r="F25">
         <v>61.36717049200722</v>
       </c>
       <c r="G25">
-        <v>17.47527523791752</v>
+        <v>21.15755427007526</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>29.85179544256341</v>
+      </c>
+      <c r="C26">
         <v>34.32136371624392</v>
-      </c>
-      <c r="C26">
-        <v>29.85179544256341</v>
       </c>
       <c r="D26">
         <v>2.913637139443591</v>
       </c>
       <c r="E26">
-        <v>20.90558766859345</v>
+        <v>18.18311567829872</v>
       </c>
       <c r="F26">
         <v>60.91129665310783</v>
       </c>
       <c r="G26">
-        <v>18.18311567829872</v>
+        <v>20.90558766859345</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>28.27412513255567</v>
+      </c>
+      <c r="C27">
         <v>32.56892895015907</v>
-      </c>
-      <c r="C27">
-        <v>28.27412513255567</v>
       </c>
       <c r="D27">
         <v>3.07041107041107</v>
       </c>
       <c r="E27">
-        <v>20.24888742376793</v>
+        <v>17.57870446678754</v>
       </c>
       <c r="F27">
         <v>62.17240810944454</v>
       </c>
       <c r="G27">
-        <v>17.57870446678754</v>
+        <v>20.24888742376793</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>29.58186791715514</v>
+      </c>
+      <c r="C28">
         <v>50.29308323563892</v>
-      </c>
-      <c r="C28">
-        <v>29.58186791715514</v>
       </c>
       <c r="D28">
         <v>1.988344988344988</v>
       </c>
       <c r="E28">
-        <v>27.96002606995438</v>
+        <v>16.44579621985661</v>
       </c>
       <c r="F28">
         <v>55.594177710189</v>
       </c>
       <c r="G28">
-        <v>16.44579621985661</v>
+        <v>27.96002606995438</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>27.22836694860117</v>
+      </c>
+      <c r="C29">
         <v>42.4202992843201</v>
-      </c>
-      <c r="C29">
-        <v>27.22836694860117</v>
       </c>
       <c r="D29">
         <v>2.357361963190184</v>
       </c>
       <c r="E29">
-        <v>25.00479386385426</v>
+        <v>16.04985618408437</v>
       </c>
       <c r="F29">
         <v>58.94534995206136</v>
       </c>
       <c r="G29">
-        <v>16.04985618408437</v>
+        <v>25.00479386385426</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.95155709342561</v>
+      </c>
+      <c r="C30">
         <v>44.20415224913495</v>
-      </c>
-      <c r="C30">
-        <v>25.95155709342561</v>
       </c>
       <c r="D30">
         <v>2.262230919765166</v>
       </c>
       <c r="E30">
-        <v>25.97864768683274</v>
+        <v>15.25165226232842</v>
       </c>
       <c r="F30">
         <v>58.76970005083884</v>
       </c>
       <c r="G30">
-        <v>15.25165226232842</v>
+        <v>25.97864768683274</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>29.0627321940346</v>
+      </c>
+      <c r="C31">
         <v>35.94098291051905</v>
-      </c>
-      <c r="C31">
-        <v>29.0627321940346</v>
       </c>
       <c r="D31">
         <v>2.782339043118724</v>
       </c>
       <c r="E31">
-        <v>21.78192344805404</v>
+        <v>17.613380508202</v>
       </c>
       <c r="F31">
         <v>60.60469604374398</v>
       </c>
       <c r="G31">
-        <v>17.613380508202</v>
+        <v>21.78192344805404</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>27.53734939759036</v>
+      </c>
+      <c r="C32">
         <v>37.77349397590361</v>
-      </c>
-      <c r="C32">
-        <v>27.53734939759036</v>
       </c>
       <c r="D32">
         <v>2.647359020158204</v>
       </c>
       <c r="E32">
-        <v>22.84997959302664</v>
+        <v>16.65792082094339</v>
       </c>
       <c r="F32">
         <v>60.49209958602997</v>
       </c>
       <c r="G32">
-        <v>16.65792082094339</v>
+        <v>22.84997959302664</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>26.69619630176475</v>
+      </c>
+      <c r="C33">
         <v>43.81635379315194</v>
-      </c>
-      <c r="C33">
-        <v>26.69619630176475</v>
       </c>
       <c r="D33">
         <v>2.282252888318357</v>
       </c>
       <c r="E33">
-        <v>25.69684974435098</v>
+        <v>15.65644070592116</v>
       </c>
       <c r="F33">
         <v>58.64670954972785</v>
       </c>
       <c r="G33">
-        <v>15.65644070592116</v>
+        <v>25.69684974435098</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>40.12318521777387</v>
+      </c>
+      <c r="C34">
         <v>21.71139463264408</v>
-      </c>
-      <c r="C34">
-        <v>40.12318521777387</v>
       </c>
       <c r="D34">
         <v>4.605876393110436</v>
       </c>
       <c r="E34">
-        <v>13.41579448144624</v>
+        <v>24.79271442163925</v>
       </c>
       <c r="F34">
         <v>61.79149109691451</v>
       </c>
       <c r="G34">
-        <v>24.79271442163925</v>
+        <v>13.41579448144624</v>
       </c>
     </row>
   </sheetData>
